--- a/E/BCD01D.xlsx
+++ b/E/BCD01D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="248">
   <si>
     <t/>
   </si>
@@ -73,22 +73,43 @@
     <t>RT,(E-4B)</t>
   </si>
   <si>
+    <t>20121413</t>
+  </si>
+  <si>
+    <t>KDMO B.WP ALOE 2X50S</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
     <t>20115153</t>
   </si>
   <si>
     <t>KODOMO B.WIPE A/B50S</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20121413</t>
-  </si>
-  <si>
-    <t>KDMO B.WP ALOE 2X50S</t>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20132821</t>
+  </si>
+  <si>
+    <t>YNKN WIPE HND&amp;MTH2'S</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20132820</t>
+  </si>
+  <si>
+    <t>YNKN WIPE ANTIBCT2'S</t>
+  </si>
+  <si>
+    <t>9</t>
   </si>
   <si>
     <t>20101378</t>
@@ -97,7 +118,58 @@
     <t>KODOMO B.WIPE PNK 50</t>
   </si>
   <si>
-    <t>7</t>
+    <t>10</t>
+  </si>
+  <si>
+    <t>20140018</t>
+  </si>
+  <si>
+    <t>IDM BB.WIPE RM 2X50S</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20138272</t>
+  </si>
+  <si>
+    <t>LRST BB.WIPE SB 2X50</t>
+  </si>
+  <si>
+    <t>20138273</t>
+  </si>
+  <si>
+    <t>LRST BB.WIPE AF 2X50</t>
+  </si>
+  <si>
+    <t>20001546</t>
+  </si>
+  <si>
+    <t>MITU TIS.G/P BLU2X50</t>
+  </si>
+  <si>
+    <t>20071105</t>
+  </si>
+  <si>
+    <t>MITU GP PURPLE 2X50S</t>
+  </si>
+  <si>
+    <t>20087203</t>
+  </si>
+  <si>
+    <t>CSSN BW FRS&amp;N 2/3X45</t>
+  </si>
+  <si>
+    <t>20113913</t>
+  </si>
+  <si>
+    <t>MY/B WIPES ANTBC 2'S</t>
+  </si>
+  <si>
+    <t>20082445</t>
+  </si>
+  <si>
+    <t>MP BB WIPES N/FR BDD</t>
   </si>
   <si>
     <t>20138144</t>
@@ -106,52 +178,10 @@
     <t>KODOMO WPS H&amp;M 2X50S</t>
   </si>
   <si>
-    <t>20132820</t>
-  </si>
-  <si>
-    <t>YNKN WIPE ANTIBCT2'S</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20132821</t>
-  </si>
-  <si>
-    <t>YNKN WIPE HND&amp;MTH2'S</t>
-  </si>
-  <si>
-    <t>20140018</t>
-  </si>
-  <si>
-    <t>IDM BB.WIPE RM 2X50S</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20138272</t>
-  </si>
-  <si>
-    <t>LRST BB.WIPE SB 2X50</t>
-  </si>
-  <si>
-    <t>20138273</t>
-  </si>
-  <si>
-    <t>LRST BB.WIPE AF 2X50</t>
-  </si>
-  <si>
-    <t>20001546</t>
-  </si>
-  <si>
-    <t>MITU TIS.G/P BLU2X50</t>
-  </si>
-  <si>
-    <t>20071105</t>
-  </si>
-  <si>
-    <t>MITU GP PURPLE 2X50S</t>
+    <t>20035113</t>
+  </si>
+  <si>
+    <t>MITU WIPE BLUE BB 40</t>
   </si>
   <si>
     <t>20001061</t>
@@ -160,10 +190,7 @@
     <t>MITU G/P PINK 2X50'S</t>
   </si>
   <si>
-    <t>20035113</t>
-  </si>
-  <si>
-    <t>MITU WIPE BLUE BB 40</t>
+    <t>11</t>
   </si>
   <si>
     <t>20016864</t>
@@ -172,22 +199,7 @@
     <t>CSSN BW RFRSH 2/3X45</t>
   </si>
   <si>
-    <t>20087203</t>
-  </si>
-  <si>
-    <t>CSSN BW FRS&amp;N 2/3X45</t>
-  </si>
-  <si>
-    <t>20113913</t>
-  </si>
-  <si>
-    <t>MY/B WIPES ANTBC 2'S</t>
-  </si>
-  <si>
-    <t>20082445</t>
-  </si>
-  <si>
-    <t>MP BB WIPES N/FR BDD</t>
+    <t>12</t>
   </si>
   <si>
     <t>20082446</t>
@@ -196,115 +208,130 @@
     <t>MP BB WIPES PRF BDD</t>
   </si>
   <si>
+    <t>13</t>
+  </si>
+  <si>
     <t>20105698</t>
   </si>
   <si>
     <t>ZWTSL KIDS BB C&amp;F280</t>
   </si>
   <si>
+    <t>20103266</t>
+  </si>
+  <si>
+    <t>MB KIDS S&amp;C H&amp;F 180</t>
+  </si>
+  <si>
+    <t>20113915</t>
+  </si>
+  <si>
+    <t>MB KIDS S&amp;C SOFT 180</t>
+  </si>
+  <si>
+    <t>20096095</t>
+  </si>
+  <si>
+    <t>KDOMO SH&amp;CON STR 200</t>
+  </si>
+  <si>
+    <t>20090400</t>
+  </si>
+  <si>
+    <t>KDOMO B.WASH STR 200</t>
+  </si>
+  <si>
+    <t>20134006</t>
+  </si>
+  <si>
+    <t>KDOMO SH&amp;CON CHRY200</t>
+  </si>
+  <si>
+    <t>20090401</t>
+  </si>
+  <si>
+    <t>KDOMO SH&amp;CON BLU 200</t>
+  </si>
+  <si>
+    <t>20113805</t>
+  </si>
+  <si>
+    <t>KDOMO B.WASH ORG 200</t>
+  </si>
+  <si>
+    <t>20143473</t>
+  </si>
+  <si>
+    <t>B&amp;B S&amp;C GLY SH200+50</t>
+  </si>
+  <si>
+    <t>20143472</t>
+  </si>
+  <si>
+    <t>BB HAIR&amp;BW PMP240+60</t>
+  </si>
+  <si>
+    <t>20135607</t>
+  </si>
+  <si>
+    <t>MB KIDS HBC LVELY100</t>
+  </si>
+  <si>
+    <t>20113917</t>
+  </si>
+  <si>
+    <t>MB KIDS HBC SWT 100</t>
+  </si>
+  <si>
+    <t>20113918</t>
+  </si>
+  <si>
+    <t>MB KIDS HBC FRSH100</t>
+  </si>
+  <si>
+    <t>20008706</t>
+  </si>
+  <si>
+    <t>MASTER CLG SPRMN 100</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20130478</t>
+  </si>
+  <si>
+    <t>DOREMI COLG GLACR100</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20143470</t>
+  </si>
+  <si>
+    <t>B&amp;B SPRAY CLGNE80+20</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
     <t>20000600</t>
   </si>
   <si>
     <t>ESKULIN SHP ARIEL200</t>
   </si>
   <si>
+    <t>17</t>
+  </si>
+  <si>
     <t>20074300</t>
   </si>
   <si>
     <t>ESKLN HR&amp;BDY S&amp;P 280</t>
   </si>
   <si>
-    <t>20103266</t>
-  </si>
-  <si>
-    <t>MB KIDS S&amp;C H&amp;F 180</t>
-  </si>
-  <si>
-    <t>20113915</t>
-  </si>
-  <si>
-    <t>MB KIDS S&amp;C SOFT 180</t>
-  </si>
-  <si>
-    <t>20096095</t>
-  </si>
-  <si>
-    <t>KDOMO SH&amp;CON STR 200</t>
-  </si>
-  <si>
-    <t>20134006</t>
-  </si>
-  <si>
-    <t>KDOMO SH&amp;CON CHRY200</t>
-  </si>
-  <si>
-    <t>20090401</t>
-  </si>
-  <si>
-    <t>KDOMO SH&amp;CON BLU 200</t>
-  </si>
-  <si>
-    <t>20090400</t>
-  </si>
-  <si>
-    <t>KDOMO B.WASH STR 200</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20113805</t>
-  </si>
-  <si>
-    <t>KDOMO B.WASH ORG 200</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20135607</t>
-  </si>
-  <si>
-    <t>MB KIDS HBC LVELY100</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20113917</t>
-  </si>
-  <si>
-    <t>MB KIDS HBC SWT 100</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>20113918</t>
-  </si>
-  <si>
-    <t>MB KIDS HBC FRSH100</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>20008706</t>
-  </si>
-  <si>
-    <t>MASTER CLG SPRMN 100</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>20130478</t>
-  </si>
-  <si>
-    <t>DOREMI COLG GLACR100</t>
-  </si>
-  <si>
-    <t>15</t>
+    <t>18</t>
   </si>
   <si>
     <t>20135794</t>
@@ -313,18 +340,18 @@
     <t>MY BB SOAP SWT.FLO75</t>
   </si>
   <si>
+    <t>20132819</t>
+  </si>
+  <si>
+    <t>BLGIO PMDE BBLGUM 40</t>
+  </si>
+  <si>
     <t>20071630</t>
   </si>
   <si>
     <t>JOHNSON SHP SHNY 100</t>
   </si>
   <si>
-    <t>20132819</t>
-  </si>
-  <si>
-    <t>BLGIO PMDE BBLGUM 40</t>
-  </si>
-  <si>
     <t>20002133</t>
   </si>
   <si>
@@ -448,148 +475,145 @@
     <t>FORMULA PG+SK BL STR</t>
   </si>
   <si>
+    <t>10017886</t>
+  </si>
+  <si>
+    <t>ORAL B S/G MCKY SOFT</t>
+  </si>
+  <si>
+    <t>20044538</t>
+  </si>
+  <si>
+    <t>HUKI DOT SLC NPL.3/L</t>
+  </si>
+  <si>
+    <t>10019114</t>
+  </si>
+  <si>
+    <t>PIGEON SL.PACIFIER 2</t>
+  </si>
+  <si>
+    <t>20062263</t>
+  </si>
+  <si>
+    <t>PIGEON PRS NPL L 3'S</t>
+  </si>
+  <si>
+    <t>20128874</t>
+  </si>
+  <si>
+    <t>P/A TEAT F/F NRML 2S</t>
+  </si>
+  <si>
     <t>10014741</t>
   </si>
   <si>
     <t>FORMULA PG+SK BL ORG</t>
   </si>
   <si>
-    <t>10017886</t>
-  </si>
-  <si>
-    <t>ORAL B S/G MCKY SOFT</t>
-  </si>
-  <si>
-    <t>20044538</t>
-  </si>
-  <si>
-    <t>HUKI DOT SLC NPL.3/L</t>
-  </si>
-  <si>
-    <t>10019114</t>
-  </si>
-  <si>
-    <t>PIGEON SL.PACIFIER 2</t>
-  </si>
-  <si>
-    <t>20062263</t>
-  </si>
-  <si>
-    <t>PIGEON PRS NPL L 3'S</t>
-  </si>
-  <si>
-    <t>20128874</t>
-  </si>
-  <si>
-    <t>P/A TEAT F/F NRML 2S</t>
+    <t>10033930</t>
+  </si>
+  <si>
+    <t>CUSSON B/CRM SOFT50</t>
+  </si>
+  <si>
+    <t>20116527</t>
+  </si>
+  <si>
+    <t>ZWITSAL F&amp;B CREAM 50</t>
+  </si>
+  <si>
+    <t>PT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20133137</t>
+  </si>
+  <si>
+    <t>MY BB FC&amp;BDY NOURI50</t>
+  </si>
+  <si>
+    <t>20071629</t>
+  </si>
+  <si>
+    <t>JHNSON COLG SLDE 100</t>
+  </si>
+  <si>
+    <t>20053295</t>
+  </si>
+  <si>
+    <t>JHNSN COLG HPY/B 100</t>
+  </si>
+  <si>
+    <t>20013772</t>
+  </si>
+  <si>
+    <t>JOHNSON COLG SUMR100</t>
+  </si>
+  <si>
+    <t>10003369</t>
+  </si>
+  <si>
+    <t>JOHNSON BABY OIL 125</t>
+  </si>
+  <si>
+    <t>10038388</t>
+  </si>
+  <si>
+    <t>JOHNSON BABY OIL 50M</t>
+  </si>
+  <si>
+    <t>20133138</t>
+  </si>
+  <si>
+    <t>MY BABY BB/OIL PLS90</t>
+  </si>
+  <si>
+    <t>20035884</t>
+  </si>
+  <si>
+    <t>CUSSONS HL.NAT KM100</t>
+  </si>
+  <si>
+    <t>10028608</t>
+  </si>
+  <si>
+    <t>CUSSONS B/OIL SFT100</t>
+  </si>
+  <si>
+    <t>20004868</t>
+  </si>
+  <si>
+    <t>JOHNSON LOTN REG 100</t>
+  </si>
+  <si>
+    <t>20099248</t>
+  </si>
+  <si>
+    <t>LCTACYD BB.LIQ SP 60</t>
+  </si>
+  <si>
+    <t>20123404</t>
+  </si>
+  <si>
+    <t>ZWTSAL BB ANBACT 200</t>
+  </si>
+  <si>
+    <t>20009872</t>
+  </si>
+  <si>
+    <t>ZWITSAL B/B M.HN 200</t>
+  </si>
+  <si>
+    <t>10033236</t>
+  </si>
+  <si>
+    <t>ZWTSL B/BTH HB AV200</t>
   </si>
   <si>
     <t>10011772</t>
   </si>
   <si>
     <t>CUSSONS B/CRM MILD50</t>
-  </si>
-  <si>
-    <t>10033930</t>
-  </si>
-  <si>
-    <t>CUSSON B/CRM SOFT50</t>
-  </si>
-  <si>
-    <t>20116527</t>
-  </si>
-  <si>
-    <t>ZWITSAL F&amp;B CREAM 50</t>
-  </si>
-  <si>
-    <t>PT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20133137</t>
-  </si>
-  <si>
-    <t>MY BB FC&amp;BDY NOURI50</t>
-  </si>
-  <si>
-    <t>20071629</t>
-  </si>
-  <si>
-    <t>JHNSON COLG SLDE 100</t>
-  </si>
-  <si>
-    <t>20053295</t>
-  </si>
-  <si>
-    <t>JHNSN COLG HPY/B 100</t>
-  </si>
-  <si>
-    <t>20013772</t>
-  </si>
-  <si>
-    <t>JOHNSON COLG SUMR100</t>
-  </si>
-  <si>
-    <t>10003369</t>
-  </si>
-  <si>
-    <t>JOHNSON BABY OIL 125</t>
-  </si>
-  <si>
-    <t>10038388</t>
-  </si>
-  <si>
-    <t>JOHNSON BABY OIL 50M</t>
-  </si>
-  <si>
-    <t>20133138</t>
-  </si>
-  <si>
-    <t>MY BABY BB/OIL PLS90</t>
-  </si>
-  <si>
-    <t>20035884</t>
-  </si>
-  <si>
-    <t>CUSSONS HL.NAT KM100</t>
-  </si>
-  <si>
-    <t>10028608</t>
-  </si>
-  <si>
-    <t>CUSSONS B/OIL SFT100</t>
-  </si>
-  <si>
-    <t>20004868</t>
-  </si>
-  <si>
-    <t>JOHNSON LOTN REG 100</t>
-  </si>
-  <si>
-    <t>20099248</t>
-  </si>
-  <si>
-    <t>LCTACYD BB.LIQ SP 60</t>
-  </si>
-  <si>
-    <t>20123404</t>
-  </si>
-  <si>
-    <t>ZWTSAL BB ANBACT 200</t>
-  </si>
-  <si>
-    <t>20009872</t>
-  </si>
-  <si>
-    <t>ZWITSAL B/B M.HN 200</t>
-  </si>
-  <si>
-    <t>10033236</t>
-  </si>
-  <si>
-    <t>ZWTSL B/BTH HB AV200</t>
-  </si>
-  <si>
-    <t>16</t>
   </si>
   <si>
     <t>20005584</t>
@@ -1123,7 +1147,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F107"/>
+  <dimension ref="A1:F110"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1288,7 +1312,7 @@
         <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>23</v>
@@ -1296,10 +1320,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -1308,18 +1332,18 @@
         <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -1328,7 +1352,7 @@
         <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>9</v>
@@ -1336,10 +1360,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -1348,38 +1372,38 @@
         <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="F12" s="1" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -1388,7 +1412,7 @@
         <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>38</v>
@@ -1396,10 +1420,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -1408,7 +1432,7 @@
         <v>8</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>38</v>
@@ -1416,10 +1440,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -1428,18 +1452,18 @@
         <v>8</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -1448,18 +1472,18 @@
         <v>8</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -1468,18 +1492,18 @@
         <v>8</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -1488,18 +1512,18 @@
         <v>8</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -1508,18 +1532,18 @@
         <v>8</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -1528,18 +1552,18 @@
         <v>8</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -1548,18 +1572,18 @@
         <v>8</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -1568,18 +1592,18 @@
         <v>8</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -1588,18 +1612,18 @@
         <v>8</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -1608,7 +1632,7 @@
         <v>8</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>38</v>
@@ -1616,10 +1640,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -1636,10 +1660,10 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
@@ -1656,10 +1680,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -1676,10 +1700,10 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -1691,15 +1715,15 @@
         <v>15</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -1711,15 +1735,15 @@
         <v>18</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -1736,10 +1760,10 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -1748,7 +1772,7 @@
         <v>12</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>23</v>
@@ -1756,10 +1780,10 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
@@ -1768,7 +1792,7 @@
         <v>12</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>23</v>
@@ -1776,10 +1800,10 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
@@ -1788,18 +1812,18 @@
         <v>12</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
@@ -1808,7 +1832,7 @@
         <v>12</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>82</v>
+        <v>35</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>23</v>
@@ -1816,10 +1840,10 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
@@ -1828,7 +1852,7 @@
         <v>12</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>9</v>
@@ -1836,10 +1860,10 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -1848,7 +1872,7 @@
         <v>12</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>9</v>
@@ -1856,10 +1880,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -1868,7 +1892,7 @@
         <v>12</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>9</v>
@@ -1925,30 +1949,30 @@
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>8</v>
+        <v>103</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>9</v>
@@ -1956,19 +1980,19 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>12</v>
+        <v>106</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>9</v>
@@ -1976,10 +2000,10 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -1988,18 +2012,18 @@
         <v>15</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>106</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -2008,18 +2032,18 @@
         <v>15</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>106</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -2028,18 +2052,18 @@
         <v>15</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>106</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -2048,18 +2072,18 @@
         <v>15</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>23</v>
+        <v>115</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -2068,18 +2092,18 @@
         <v>15</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>38</v>
+        <v>115</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -2088,18 +2112,18 @@
         <v>15</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>79</v>
+        <v>22</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>23</v>
+        <v>115</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -2108,18 +2132,18 @@
         <v>15</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>82</v>
+        <v>26</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>119</v>
+        <v>23</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
@@ -2128,18 +2152,18 @@
         <v>15</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>119</v>
+        <v>38</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
@@ -2148,18 +2172,18 @@
         <v>15</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>88</v>
+        <v>32</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>119</v>
+        <v>23</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
@@ -2168,18 +2192,18 @@
         <v>15</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
@@ -2188,18 +2212,18 @@
         <v>15</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
@@ -2208,78 +2232,78 @@
         <v>15</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>38</v>
+        <v>128</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>8</v>
+        <v>94</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>23</v>
+        <v>128</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
@@ -2288,18 +2312,18 @@
         <v>18</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
@@ -2308,18 +2332,18 @@
         <v>18</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
@@ -2328,18 +2352,18 @@
         <v>18</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>5</v>
+        <v>145</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
@@ -2348,18 +2372,18 @@
         <v>18</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
@@ -2368,7 +2392,7 @@
         <v>18</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -2376,10 +2400,10 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
@@ -2388,18 +2412,18 @@
         <v>18</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
@@ -2408,18 +2432,18 @@
         <v>18</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>79</v>
+        <v>26</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>119</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
@@ -2428,18 +2452,18 @@
         <v>18</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>82</v>
+        <v>29</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>119</v>
+        <v>38</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
@@ -2448,18 +2472,18 @@
         <v>18</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
@@ -2468,78 +2492,78 @@
         <v>18</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>88</v>
+        <v>35</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>5</v>
+        <v>128</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>5</v>
+        <v>128</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>163</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
@@ -2548,18 +2572,18 @@
         <v>22</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
@@ -2568,18 +2592,18 @@
         <v>22</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>9</v>
+        <v>170</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
@@ -2588,7 +2612,7 @@
         <v>22</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>9</v>
@@ -2596,10 +2620,10 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
@@ -2608,7 +2632,7 @@
         <v>22</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>9</v>
@@ -2616,10 +2640,10 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
@@ -2628,7 +2652,7 @@
         <v>22</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>9</v>
@@ -2636,10 +2660,10 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
@@ -2648,7 +2672,7 @@
         <v>22</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>9</v>
@@ -2656,10 +2680,10 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
@@ -2668,7 +2692,7 @@
         <v>22</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>79</v>
+        <v>26</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>9</v>
@@ -2676,10 +2700,10 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
@@ -2688,18 +2712,18 @@
         <v>22</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>82</v>
+        <v>29</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
@@ -2708,18 +2732,18 @@
         <v>22</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
@@ -2728,18 +2752,18 @@
         <v>22</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>88</v>
+        <v>35</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
@@ -2748,18 +2772,18 @@
         <v>22</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>91</v>
+        <v>59</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
@@ -2768,18 +2792,18 @@
         <v>22</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
@@ -2788,18 +2812,18 @@
         <v>22</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
@@ -2808,7 +2832,7 @@
         <v>22</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>192</v>
+        <v>94</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>38</v>
@@ -2816,19 +2840,19 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>4</v>
+        <v>97</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>38</v>
@@ -2836,119 +2860,119 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>197</v>
+        <v>38</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>12</v>
+        <v>103</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>9</v>
+        <v>205</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>9</v>
@@ -2956,19 +2980,19 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>9</v>
@@ -2976,39 +3000,39 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>79</v>
+        <v>22</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>82</v>
+        <v>26</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>9</v>
@@ -3016,19 +3040,19 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>9</v>
@@ -3036,39 +3060,39 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>9</v>
@@ -3076,19 +3100,19 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>9</v>
@@ -3096,79 +3120,79 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>38</v>
@@ -3176,101 +3200,161 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>79</v>
+        <v>22</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>82</v>
+        <v>26</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>88</v>
+        <v>32</v>
       </c>
       <c r="F107" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F110" s="1" t="s">
         <v>5</v>
       </c>
     </row>
